--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -3618,7 +3618,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -6932,7 +6932,7 @@
           <t>C | 318呎 (1房)
 $575万
 $18,069/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6955,7 +6955,7 @@
           <t>A | 304呎 (1房)
 $534万
 $17,566/呎
-(26年-06月-26日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -7002,7 +7002,7 @@
           <t>B | 286呎 (1房)
 $477万
 $16,689/呎
-(26年-07月-20日)</t>
+(26年-07月-21日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -7010,7 +7010,7 @@
           <t>C | 318呎 (1房)
 $563万
 $17,714/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7041,7 +7041,7 @@
           <t>B | 286呎 (1房)
 $476万
 $16,626/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7072,7 +7072,7 @@
           <t>A | 304呎 (1房)
 $523万
 $17,207/呎
-(26年-06月-26日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -7096,7 +7096,7 @@
           <t>D | 218呎 (开放式)
 $415万
 $19,028/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
           <t>A | 304呎 (1房)
 $513万
 $16,865/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -7127,7 +7127,7 @@
           <t>C | 318呎 (1房)
 $547万
 $17,192/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7135,7 +7135,7 @@
           <t>D | 218呎 (开放式)
 $411万
 $18,835/呎
-(26年-06月-28日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
           <t>B | 286呎 (1房)
 $458万
 $15,997/呎
-(26年-07月-08日)</t>
+(26年-07月-30日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -7205,7 +7205,7 @@
           <t>C | 318呎 (1房)
 $541万
 $17,022/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -7213,7 +7213,7 @@
           <t>D | 218呎 (开放式)
 $407万
 $18,651/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
           <t>D | 218呎 (开放式)
 $378万
 $17,339/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
     </row>

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3675,34 +3675,34 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>5359000</v>
+        <v>4931000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>18738</v>
+        <v>17241</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>4930280</v>
+        <v>4931000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>17239</v>
+        <v>17241</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>尊盈投資計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6919,12 +6919,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
-$536万
-$18,738/呎
-(在售)</t>
+$493万
+$17,241/呎
+(26年-08月-09日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 674呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 572呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 674呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 572呎 (2房)
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -3419,34 +3419,34 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>5380000</v>
+        <v>4950000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>18811</v>
+        <v>17308</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>4949600</v>
+        <v>4950000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>17306</v>
+        <v>17308</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>尊盈投資計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6880,12 +6880,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
-$538万
-$18,811/呎
-(在售)</t>
+$495万
+$17,308/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 674呎 (2房)
+          <t>A | 673呎 (2房)
 -
 -
 (待售)</t>
@@ -6521,7 +6521,7 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 572呎 (2房)
+          <t>C | 603呎 (2房)
 -
 -
 (待售)</t>

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 673呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 603呎 (2房)
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 673呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 603呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 673呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 603呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 673呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 603呎 (2房)
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>A | 673呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>C | 603呎 (2房)
+      <c r="D5" s="20" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 673呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 603呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6888,7 +6888,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6924,7 +6924,7 @@
           <t>B | 286呎 (1房)
 $493万
 $17,241/呎
-(26年-08月-09日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -

--- a/九龙-油麻地-原舍/原舍_销控明细表.xlsx
+++ b/九龙-油麻地-原舍/原舍_销控明细表.xlsx
@@ -266,10 +266,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -6507,52 +6507,52 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>B | 286呎 (1房)
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 673呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>D | 217呎 (开放式)
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 603呎 (2房)
 -
 -
 (待售)</t>
         </is>
       </c>
+      <c r="E5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>27&amp;28</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>A | 673呎 (2房)
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 286呎 (1房)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>C | 603呎 (2房)
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 217呎 (开放式)
 -
 -
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -6560,7 +6560,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6568,7 +6568,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6576,7 +6576,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6584,7 +6584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6599,7 +6599,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6607,7 +6607,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6615,7 +6615,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6623,7 +6623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6638,7 +6638,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6646,7 +6646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6654,7 +6654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6662,7 +6662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6677,7 +6677,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6685,7 +6685,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6693,7 +6693,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6701,7 +6701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6716,7 +6716,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6724,7 +6724,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6732,7 +6732,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6740,7 +6740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6755,7 +6755,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6763,7 +6763,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6771,7 +6771,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6779,7 +6779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6794,7 +6794,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6802,7 +6802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6810,7 +6810,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6818,7 +6818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6833,7 +6833,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6849,7 +6849,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6857,7 +6857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6872,7 +6872,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -6885,10 +6885,10 @@
           <t>B | 286呎 (1房)
 $495万
 $17,308/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+(26年-09月-03日)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6896,7 +6896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -6958,7 +6958,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -6966,7 +6966,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -6974,7 +6974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7075,7 +7075,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7114,7 +7114,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7153,7 +7153,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7231,7 +7231,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7239,7 +7239,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7262,7 +7262,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 304呎 (1房)
 -
@@ -7270,7 +7270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 -
@@ -7278,7 +7278,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 318呎 (1房)
 -
@@ -7286,7 +7286,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 218呎 (开放式)
 -
@@ -7301,7 +7301,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 267呎 (1房)
 -
@@ -7309,7 +7309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 248呎 (1房)
 -
@@ -7317,7 +7317,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 280呎 (1房)
 -
@@ -7325,7 +7325,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 180呎 (开放式)
 -
